--- a/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,11 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>source_pdf</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>validation_tier</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,16 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>validation_tier</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wy_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,11 @@
       <c r="T1" t="inlineStr">
         <is>
           <t>external_validation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
         </is>
       </c>
     </row>
